--- a/portfolio_tracker.xlsx
+++ b/portfolio_tracker.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Log" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,198 +12,46 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open Positions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closed Trades" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Learning Feedback" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Improvements" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runbook" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-  </numFmts>
-  <fonts count="30">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FF00B050"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <family val="1"/>
-      <b val="1"/>
-      <color rgb="FF00B050"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF00B050"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFD700"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00AAAAAA"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
+      <color rgb="0000B050"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="001565C0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00555555"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="0043A047"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="002E7D32"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000D47A1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00BBBBBB"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00111111"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
-      <color rgb="00A8FF60"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001565C0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00E65100"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -211,124 +60,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A3A5C"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="001A3A5C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor rgb="FFCCFFFF"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001A1A2E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F3460"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00374785"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EAF6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3E5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEBEE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000D47A1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E1E2E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C62828"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E65100"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001B5E20"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004A148C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0037474F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00004D40"/>
+        <fgColor rgb="00FFCCCC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -336,142 +82,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -482,381 +97,69 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="12" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCCCC"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1A3A5C"/>
-      <rgbColor rgb="FF00B050"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
       <rgbColor rgb="00003300"/>
@@ -875,10 +178,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -916,128 +219,234 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1053,8 +462,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W90"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:W85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -1065,7 +474,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
@@ -1075,11 +484,13 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="23" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="22"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -1196,7 +607,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-17</t>
@@ -1231,7 +642,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-17</t>
@@ -1260,13 +671,13 @@
         <v>4096</v>
       </c>
       <c r="I3" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>56.4</v>
+        <v>48</v>
       </c>
       <c r="K3" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="L3" t="n">
         <v>993.28</v>
@@ -1277,7 +688,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O3" t="n">
         <v>6.83</v>
@@ -1288,7 +699,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -1306,7 +717,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>2026-06-17</t>
@@ -1335,13 +746,13 @@
         <v>1964</v>
       </c>
       <c r="I4" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>111.1</v>
+        <v>174.9</v>
       </c>
       <c r="K4" t="n">
-        <v>5.66</v>
+        <v>8.91</v>
       </c>
       <c r="L4" t="n">
         <v>1905.08</v>
@@ -1352,7 +763,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O4" t="n">
         <v>6.67</v>
@@ -1363,7 +774,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1381,7 +792,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>2026-06-17</t>
@@ -1416,7 +827,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1451,7 +862,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1480,13 +891,13 @@
         <v>4096</v>
       </c>
       <c r="I7" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>56.4</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="L7" t="n">
         <v>993.28</v>
@@ -1497,7 +908,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O7" t="n">
         <v>6.83</v>
@@ -1508,7 +919,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1526,7 +937,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1558,7 +969,7 @@
         <v>1964</v>
       </c>
       <c r="I8" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>-76.2</v>
@@ -1575,7 +986,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O8" t="n">
         <v>6.67</v>
@@ -1586,7 +997,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1604,7 +1015,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1639,7 +1050,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1671,7 +1082,7 @@
         <v>1964</v>
       </c>
       <c r="I10" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>-76.2</v>
@@ -1688,7 +1099,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O10" t="n">
         <v>6.67</v>
@@ -1699,7 +1110,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1717,7 +1128,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1752,7 +1163,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1781,24 +1192,24 @@
         <v>2665</v>
       </c>
       <c r="I12" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>118.4</v>
+        <v>144.9</v>
       </c>
       <c r="K12" t="n">
-        <v>4.44</v>
+        <v>5.44</v>
       </c>
       <c r="L12" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O12" t="n">
         <v>6.15</v>
@@ -1809,7 +1220,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -1827,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1856,13 +1267,13 @@
         <v>4021.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>222.3</v>
+        <v>181.8</v>
       </c>
       <c r="K13" t="n">
-        <v>5.53</v>
+        <v>4.52</v>
       </c>
       <c r="L13" t="n">
         <v>1300.38</v>
@@ -1873,7 +1284,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O13" t="n">
         <v>6.23</v>
@@ -1884,7 +1295,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1902,7 +1313,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1937,7 +1348,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -1966,13 +1377,13 @@
         <v>4848</v>
       </c>
       <c r="I15" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>576.96</v>
+        <v>366</v>
       </c>
       <c r="K15" t="n">
-        <v>11.9</v>
+        <v>7.55</v>
       </c>
       <c r="L15" t="n">
         <v>195.94</v>
@@ -1983,7 +1394,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O15" t="n">
         <v>6.72</v>
@@ -1994,7 +1405,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -2012,7 +1423,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2044,7 +1455,7 @@
         <v>2665</v>
       </c>
       <c r="I16" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>-15.5</v>
@@ -2053,15 +1464,15 @@
         <v>-0.6</v>
       </c>
       <c r="L16" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O16" t="n">
         <v>6.15</v>
@@ -2072,7 +1483,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -2090,7 +1501,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2119,13 +1530,13 @@
         <v>4021.8</v>
       </c>
       <c r="I17" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>222.3</v>
+        <v>181.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5.53</v>
+        <v>4.52</v>
       </c>
       <c r="L17" t="n">
         <v>1300.38</v>
@@ -2136,7 +1547,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O17" t="n">
         <v>6.23</v>
@@ -2147,7 +1558,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2165,7 +1576,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2200,7 +1611,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2229,13 +1640,13 @@
         <v>4848</v>
       </c>
       <c r="I19" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>576.96</v>
+        <v>366</v>
       </c>
       <c r="K19" t="n">
-        <v>11.9</v>
+        <v>7.55</v>
       </c>
       <c r="L19" t="n">
         <v>195.94</v>
@@ -2246,7 +1657,7 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O19" t="n">
         <v>6.72</v>
@@ -2257,7 +1668,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2275,7 +1686,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2307,7 +1718,7 @@
         <v>2665</v>
       </c>
       <c r="I20" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>-15.5</v>
@@ -2316,15 +1727,15 @@
         <v>-0.6</v>
       </c>
       <c r="L20" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O20" t="n">
         <v>6.15</v>
@@ -2335,7 +1746,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -2353,7 +1764,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2382,13 +1793,13 @@
         <v>3690</v>
       </c>
       <c r="I21" t="n">
-        <v>3806.8</v>
+        <v>3871</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>116.8</v>
+        <v>181</v>
       </c>
       <c r="K21" t="n">
-        <v>3.17</v>
+        <v>4.91</v>
       </c>
       <c r="L21" t="n">
         <v>1715.85</v>
@@ -2399,7 +1810,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
       <c r="O21" t="n">
         <v>6.43</v>
@@ -2410,7 +1821,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2428,7 +1839,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2463,7 +1874,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2492,13 +1903,13 @@
         <v>1964</v>
       </c>
       <c r="I23" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>111.1</v>
+        <v>174.9</v>
       </c>
       <c r="K23" t="n">
-        <v>5.66</v>
+        <v>8.91</v>
       </c>
       <c r="L23" t="n">
         <v>1905.08</v>
@@ -2509,7 +1920,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O23" t="n">
         <v>6.67</v>
@@ -2520,7 +1931,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2538,7 +1949,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2567,13 +1978,13 @@
         <v>3916.9</v>
       </c>
       <c r="I24" t="n">
-        <v>4097.6</v>
+        <v>4291.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>180.7</v>
+        <v>374.4</v>
       </c>
       <c r="K24" t="n">
-        <v>4.61</v>
+        <v>9.56</v>
       </c>
       <c r="L24" t="n">
         <v>292.26</v>
@@ -2595,7 +2006,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2613,7 +2024,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -2642,24 +2053,24 @@
         <v>3008.6</v>
       </c>
       <c r="I25" t="n">
-        <v>3346.6</v>
+        <v>3466.4</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>338</v>
+        <v>457.8</v>
       </c>
       <c r="K25" t="n">
-        <v>11.23</v>
+        <v>15.22</v>
       </c>
       <c r="L25" t="n">
-        <v>1459.17</v>
+        <v>1399</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="O25" t="n">
         <v>6.8</v>
@@ -2670,7 +2081,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -2688,7 +2099,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -2717,13 +2128,13 @@
         <v>3690</v>
       </c>
       <c r="I26" t="n">
-        <v>3806.8</v>
+        <v>3871</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>116.8</v>
+        <v>181</v>
       </c>
       <c r="K26" t="n">
-        <v>3.17</v>
+        <v>4.91</v>
       </c>
       <c r="L26" t="n">
         <v>1715.85</v>
@@ -2734,7 +2145,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
       <c r="O26" t="n">
         <v>6.43</v>
@@ -2745,7 +2156,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -2763,7 +2174,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -2795,7 +2206,7 @@
         <v>1964</v>
       </c>
       <c r="I27" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>-19.3</v>
@@ -2812,7 +2223,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O27" t="n">
         <v>6.67</v>
@@ -2823,7 +2234,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -2841,7 +2252,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -2870,13 +2281,13 @@
         <v>3916.9</v>
       </c>
       <c r="I28" t="n">
-        <v>4097.6</v>
+        <v>4291.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>180.7</v>
+        <v>374.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4.61</v>
+        <v>9.56</v>
       </c>
       <c r="L28" t="n">
         <v>292.26</v>
@@ -2898,7 +2309,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2916,7 +2327,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -2945,24 +2356,24 @@
         <v>3008.6</v>
       </c>
       <c r="I29" t="n">
-        <v>3346.6</v>
+        <v>3466.4</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>338</v>
+        <v>457.8</v>
       </c>
       <c r="K29" t="n">
-        <v>11.23</v>
+        <v>15.22</v>
       </c>
       <c r="L29" t="n">
-        <v>1459.17</v>
+        <v>1399</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N29" t="n">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="O29" t="n">
         <v>6.8</v>
@@ -2973,7 +2384,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2991,7 +2402,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3023,7 +2434,7 @@
         <v>1964</v>
       </c>
       <c r="I30" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>-19.3</v>
@@ -3040,7 +2451,7 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O30" t="n">
         <v>6.67</v>
@@ -3051,7 +2462,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3069,7 +2480,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3098,13 +2509,13 @@
         <v>2845.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2903.6</v>
+        <v>2878.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>58</v>
+        <v>33.2</v>
       </c>
       <c r="K31" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="L31" t="n">
         <v>1280.52</v>
@@ -3126,7 +2537,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3144,7 +2555,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3179,7 +2590,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3214,7 +2625,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3246,7 +2657,7 @@
         <v>1964</v>
       </c>
       <c r="I34" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>-19.3</v>
@@ -3263,7 +2674,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O34" t="n">
         <v>6.67</v>
@@ -3274,7 +2685,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3292,7 +2703,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -3327,7 +2738,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3356,13 +2767,13 @@
         <v>2845.6</v>
       </c>
       <c r="I36" t="n">
-        <v>2903.6</v>
+        <v>2878.8</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>58</v>
+        <v>33.2</v>
       </c>
       <c r="K36" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="L36" t="n">
         <v>1280.52</v>
@@ -3384,7 +2795,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3402,7 +2813,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3463,7 +2874,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3524,7 +2935,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3556,7 +2967,7 @@
         <v>1964</v>
       </c>
       <c r="I39" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>-28.2</v>
@@ -3573,7 +2984,7 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O39" t="n">
         <v>6.67</v>
@@ -3584,7 +2995,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -3602,7 +3013,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1">
+    <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3663,7 +3074,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1">
+    <row r="41">
       <c r="A41" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3695,7 +3106,7 @@
         <v>4096</v>
       </c>
       <c r="I41" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>-29.6</v>
@@ -3712,7 +3123,7 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O41" t="n">
         <v>6.83</v>
@@ -3723,7 +3134,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3741,7 +3152,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1">
+    <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3802,7 +3213,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3834,7 +3245,7 @@
         <v>4021.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>-6.6</v>
@@ -3851,7 +3262,7 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O43" t="n">
         <v>6.23</v>
@@ -3862,7 +3273,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -3880,7 +3291,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
+    <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3941,7 +3352,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45">
       <c r="A45" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -3973,7 +3384,7 @@
         <v>4848</v>
       </c>
       <c r="I45" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>-98.7</v>
@@ -3990,7 +3401,7 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O45" t="n">
         <v>6.72</v>
@@ -4001,7 +3412,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4019,7 +3430,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1">
+    <row r="46">
       <c r="A46" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4080,7 +3491,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
+    <row r="47">
       <c r="A47" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4141,7 +3552,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
+    <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4173,7 +3584,7 @@
         <v>1964</v>
       </c>
       <c r="I48" t="n">
-        <v>2075.1</v>
+        <v>2138.9</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>-28.2</v>
@@ -4190,7 +3601,7 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>6.35</v>
+        <v>6.48</v>
       </c>
       <c r="O48" t="n">
         <v>6.67</v>
@@ -4201,7 +3612,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -4219,7 +3630,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1">
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4280,7 +3691,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1">
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4312,7 +3723,7 @@
         <v>4096</v>
       </c>
       <c r="I50" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>-29.6</v>
@@ -4329,7 +3740,7 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O50" t="n">
         <v>6.83</v>
@@ -4340,7 +3751,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -4358,7 +3769,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1">
+    <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4390,7 +3801,7 @@
         <v>4848</v>
       </c>
       <c r="I51" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>-98.7</v>
@@ -4407,7 +3818,7 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O51" t="n">
         <v>6.72</v>
@@ -4418,7 +3829,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -4436,7 +3847,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4465,24 +3876,24 @@
         <v>2665</v>
       </c>
       <c r="I52" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>118.4</v>
+        <v>144.9</v>
       </c>
       <c r="K52" t="n">
-        <v>4.44</v>
+        <v>5.44</v>
       </c>
       <c r="L52" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O52" t="n">
         <v>6.15</v>
@@ -4493,7 +3904,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -4511,7 +3922,7 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4572,7 +3983,7 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
+    <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -4604,7 +4015,7 @@
         <v>4021.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>-6.6</v>
@@ -4621,7 +4032,7 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O54" t="n">
         <v>6.23</v>
@@ -4632,7 +4043,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -4650,7 +4061,7 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1">
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -4679,13 +4090,13 @@
         <v>4096</v>
       </c>
       <c r="I55" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>56.4</v>
+        <v>48</v>
       </c>
       <c r="K55" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="L55" t="n">
         <v>993.28</v>
@@ -4696,7 +4107,7 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O55" t="n">
         <v>6.83</v>
@@ -4707,7 +4118,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -4725,7 +4136,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1">
+    <row r="56">
       <c r="A56" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -4754,13 +4165,13 @@
         <v>4848</v>
       </c>
       <c r="I56" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>576.96</v>
+        <v>366</v>
       </c>
       <c r="K56" t="n">
-        <v>11.9</v>
+        <v>7.55</v>
       </c>
       <c r="L56" t="n">
         <v>195.94</v>
@@ -4771,7 +4182,7 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O56" t="n">
         <v>6.72</v>
@@ -4782,7 +4193,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -4800,7 +4211,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1">
+    <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -4832,7 +4243,7 @@
         <v>2665</v>
       </c>
       <c r="I57" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>-51.3</v>
@@ -4841,15 +4252,15 @@
         <v>-1.93</v>
       </c>
       <c r="L57" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O57" t="n">
         <v>6.15</v>
@@ -4860,7 +4271,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -4878,7 +4289,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
+    <row r="58">
       <c r="A58" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -4913,7 +4324,7 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
+    <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -4942,13 +4353,13 @@
         <v>4021.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>222.3</v>
+        <v>181.8</v>
       </c>
       <c r="K59" t="n">
-        <v>5.53</v>
+        <v>4.52</v>
       </c>
       <c r="L59" t="n">
         <v>1300.38</v>
@@ -4959,7 +4370,7 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O59" t="n">
         <v>6.23</v>
@@ -4970,7 +4381,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -4988,7 +4399,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1">
+    <row r="60">
       <c r="A60" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5020,7 +4431,7 @@
         <v>2665</v>
       </c>
       <c r="I60" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>-51.3</v>
@@ -5029,15 +4440,15 @@
         <v>-1.93</v>
       </c>
       <c r="L60" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O60" t="n">
         <v>6.15</v>
@@ -5048,7 +4459,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -5066,7 +4477,7 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
+    <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5085,51 +4496,11 @@
           <t>BUY-PENDING</t>
         </is>
       </c>
-      <c r="E61" t="n">
-        <v>1331.9</v>
-      </c>
-      <c r="G61" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" t="n">
-        <v>2663.8</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2709.2</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1291.94</v>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>TIGHT</t>
         </is>
       </c>
-      <c r="N61" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="O61" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>ACCUMULATE 💚</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>14</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>BUY-PENDING</t>
@@ -5141,7 +4512,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1">
+    <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5176,7 +4547,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1">
+    <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5205,13 +4576,13 @@
         <v>4840</v>
       </c>
       <c r="I63" t="n">
-        <v>4980.4</v>
+        <v>4992.6</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>140.4</v>
+        <v>152.6</v>
       </c>
       <c r="K63" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="L63" t="n">
         <v>2347.4</v>
@@ -5222,7 +4593,7 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="O63" t="n">
         <v>6.48</v>
@@ -5233,7 +4604,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -5251,7 +4622,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15" customHeight="1">
+    <row r="64">
       <c r="A64" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5280,24 +4651,24 @@
         <v>3780</v>
       </c>
       <c r="I64" t="n">
-        <v>3851.6</v>
+        <v>3840.8</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="K64" t="n">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="L64" t="n">
-        <v>1833.3</v>
+        <v>1757.7</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6.3</v>
+        <v>6.74</v>
       </c>
       <c r="O64" t="n">
         <v>6.25</v>
@@ -5308,7 +4679,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -5326,7 +4697,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
+    <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -5361,7 +4732,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1">
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5380,63 +4751,18 @@
           <t>BUY-FILLED</t>
         </is>
       </c>
-      <c r="E66" t="n">
-        <v>1331.9</v>
-      </c>
-      <c r="G66" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" t="n">
-        <v>2663.8</v>
-      </c>
-      <c r="I66" t="n">
-        <v>2709.2</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1291.94</v>
-      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>TIGHT</t>
         </is>
       </c>
-      <c r="N66" t="n">
-        <v>8.039999999999999</v>
-      </c>
-      <c r="O66" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>ACCUMULATE 💚</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>14</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
       <c r="S66" t="inlineStr">
         <is>
           <t>BUY-FILLED</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
+    </row>
+    <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5491,13 +4817,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
+    </row>
+    <row r="68">
       <c r="A68" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5529,7 +4850,7 @@
         <v>4840</v>
       </c>
       <c r="I68" t="n">
-        <v>4980.4</v>
+        <v>4992.6</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>-31.4</v>
@@ -5546,7 +4867,7 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="O68" t="n">
         <v>6.48</v>
@@ -5557,7 +4878,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -5569,13 +4890,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1">
+    </row>
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5607,7 +4923,7 @@
         <v>3780</v>
       </c>
       <c r="I69" t="n">
-        <v>3851.6</v>
+        <v>3840.8</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>-34.3</v>
@@ -5616,15 +4932,15 @@
         <v>-1.82</v>
       </c>
       <c r="L69" t="n">
-        <v>1833.3</v>
+        <v>1757.7</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>6.3</v>
+        <v>6.74</v>
       </c>
       <c r="O69" t="n">
         <v>6.25</v>
@@ -5635,7 +4951,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -5647,13 +4963,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1">
+    </row>
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5708,13 +5019,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
+    </row>
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5746,7 +5052,7 @@
         <v>3916.9</v>
       </c>
       <c r="I71" t="n">
-        <v>4097.6</v>
+        <v>4291.3</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>-7.8</v>
@@ -5774,7 +5080,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -5786,13 +5092,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
+    </row>
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5847,13 +5148,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
+    </row>
+    <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5908,13 +5204,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
+    </row>
+    <row r="74">
       <c r="A74" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -5946,7 +5237,7 @@
         <v>4840</v>
       </c>
       <c r="I74" t="n">
-        <v>4980.4</v>
+        <v>4992.6</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>-31.4</v>
@@ -5963,7 +5254,7 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="O74" t="n">
         <v>6.48</v>
@@ -5974,7 +5265,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -5986,13 +5277,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
+    </row>
+    <row r="75">
       <c r="A75" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6024,7 +5310,7 @@
         <v>3780</v>
       </c>
       <c r="I75" t="n">
-        <v>3851.6</v>
+        <v>3840.8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>-34.3</v>
@@ -6033,15 +5319,15 @@
         <v>-1.82</v>
       </c>
       <c r="L75" t="n">
-        <v>1833.3</v>
+        <v>1757.7</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>6.3</v>
+        <v>6.74</v>
       </c>
       <c r="O75" t="n">
         <v>6.25</v>
@@ -6052,7 +5338,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -6064,13 +5350,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1">
+    </row>
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6125,13 +5406,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
+    </row>
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6160,24 +5436,24 @@
         <v>2665</v>
       </c>
       <c r="I77" t="n">
-        <v>2783.4</v>
+        <v>2809.9</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>118.4</v>
+        <v>144.9</v>
       </c>
       <c r="K77" t="n">
-        <v>4.44</v>
+        <v>5.44</v>
       </c>
       <c r="L77" t="n">
-        <v>2585.05</v>
+        <v>2478.45</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>5.85</v>
+        <v>6.73</v>
       </c>
       <c r="O77" t="n">
         <v>6.15</v>
@@ -6188,7 +5464,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -6200,13 +5476,8 @@
           <t>BUY-PENDING</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
+    </row>
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6235,13 +5506,8 @@
           <t>BUY-PENDING</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
+    </row>
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6273,7 +5539,7 @@
         <v>3916.9</v>
       </c>
       <c r="I79" t="n">
-        <v>4097.6</v>
+        <v>4291.3</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>-7.8</v>
@@ -6301,7 +5567,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -6313,13 +5579,8 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
+    </row>
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6348,13 +5609,13 @@
         <v>3967.5</v>
       </c>
       <c r="I80" t="n">
-        <v>4146.5</v>
+        <v>4124.75</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>179</v>
+        <v>157.25</v>
       </c>
       <c r="K80" t="n">
-        <v>4.51</v>
+        <v>3.96</v>
       </c>
       <c r="L80" t="n">
         <v>769.6900000000001</v>
@@ -6365,7 +5626,7 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>6.95</v>
+        <v>6.78</v>
       </c>
       <c r="O80" t="n">
         <v>7.3</v>
@@ -6376,7 +5637,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -6388,13 +5649,8 @@
           <t>BUY-PENDING</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15" customHeight="1">
+    </row>
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -6449,85 +5705,94 @@
           <t>SELL-STOP</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
+    </row>
+    <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B82" t="n">
+        <v>17</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>BUY-FILLED</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>312</v>
+      </c>
+      <c r="G82" t="n">
         <v>14</v>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>SELL-STOP</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="F82" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="G82" t="n">
-        <v>257</v>
-      </c>
       <c r="H82" t="n">
-        <v>3716.22</v>
+        <v>4368</v>
+      </c>
+      <c r="I82" t="n">
+        <v>4336.5</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>-156.77</v>
+        <v>-31.5</v>
       </c>
       <c r="K82" t="n">
-        <v>-4.22</v>
+        <v>-0.72</v>
+      </c>
+      <c r="L82" t="n">
+        <v>302.64</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>TIGHT</t>
         </is>
       </c>
+      <c r="N82" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O82" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>HOLD ⚖️</t>
+        </is>
+      </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>SELL-STOP</t>
+          <t>BUY-FILLED</t>
         </is>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1">
+          <t>CAUTIOUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DABUR</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -6547,22 +5812,22 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
+          <t>CAUTIOUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -6582,22 +5847,22 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
+          <t>CAUTIOUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -6617,281 +5882,12 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>14</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>BPCL</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>BUY-PENDING</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>BUY-PENDING</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>14</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>MARUTI</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>BUY-PENDING</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>BUY-PENDING</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B88" s="71" t="n">
-        <v>15</v>
-      </c>
-      <c r="C88" s="72" t="inlineStr">
-        <is>
-          <t>DABUR</t>
-        </is>
-      </c>
-      <c r="D88" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="E88" s="72" t="n">
-        <v>370.14</v>
-      </c>
-      <c r="F88" s="72" t="n"/>
-      <c r="G88" s="72" t="n">
-        <v>7</v>
-      </c>
-      <c r="H88" s="72" t="n">
-        <v>2591</v>
-      </c>
-      <c r="I88" s="72" t="n"/>
-      <c r="J88" s="72" t="n"/>
-      <c r="K88" s="72" t="n"/>
-      <c r="L88" s="72" t="n"/>
-      <c r="M88" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="N88" s="72" t="n"/>
-      <c r="O88" s="72" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="P88" s="72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="Q88" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="72" t="inlineStr">
-        <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="S88" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="W88" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B89" s="71" t="n">
-        <v>15</v>
-      </c>
-      <c r="C89" s="72" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="D89" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="E89" s="72" t="n">
-        <v>1223</v>
-      </c>
-      <c r="F89" s="72" t="n"/>
-      <c r="G89" s="72" t="n">
-        <v>2</v>
-      </c>
-      <c r="H89" s="72" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I89" s="72" t="n"/>
-      <c r="J89" s="72" t="n"/>
-      <c r="K89" s="72" t="n"/>
-      <c r="L89" s="72" t="n"/>
-      <c r="M89" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="N89" s="72" t="n"/>
-      <c r="O89" s="72" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="P89" s="72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="Q89" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="72" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-      <c r="S89" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="W89" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B90" s="71" t="n">
-        <v>15</v>
-      </c>
-      <c r="C90" s="72" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="D90" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="E90" s="72" t="n">
-        <v>2446</v>
-      </c>
-      <c r="F90" s="72" t="n"/>
-      <c r="G90" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" s="72" t="n">
-        <v>2446</v>
-      </c>
-      <c r="I90" s="72" t="n"/>
-      <c r="J90" s="72" t="n"/>
-      <c r="K90" s="72" t="n"/>
-      <c r="L90" s="72" t="n"/>
-      <c r="M90" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="N90" s="72" t="n"/>
-      <c r="O90" s="72" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="P90" s="72" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="Q90" s="72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="72" t="inlineStr">
-        <is>
-          <t>Pharma</t>
-        </is>
-      </c>
-      <c r="S90" s="72" t="inlineStr">
-        <is>
-          <t>FILL</t>
-        </is>
-      </c>
-      <c r="W90" s="72" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
+          <t>CAUTIOUS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -6901,15 +5897,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="8"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
@@ -6923,7 +5921,7 @@
     <col width="9" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -7020,7 +6018,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>2026-06-17</t>
@@ -7073,12 +6071,11 @@
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="S2">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>2026-06-18</t>
@@ -7136,12 +6133,11 @@
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="S3">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>2026-06-19</t>
@@ -7199,12 +6195,11 @@
           <t>CARTRADE</t>
         </is>
       </c>
-      <c r="S4">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
@@ -7262,12 +6257,11 @@
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="S5">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>2026-06-23</t>
@@ -7330,12 +6324,11 @@
           <t>IDEA</t>
         </is>
       </c>
-      <c r="S6">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>2026-06-24</t>
@@ -7393,368 +6386,187 @@
           <t>CARTRADE</t>
         </is>
       </c>
-      <c r="S7">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>99991.28</v>
       </c>
-      <c r="D8" t="n">
-        <v>42862.62</v>
-      </c>
-      <c r="E8" t="n">
-        <v>57128.66</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="D8" s="6" t="n">
+        <v>46272.98</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>53718.3</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>-51.3</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>-0.05</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="7" t="n">
         <v>-8.720000000000001</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="J8" t="n">
-        <v>19531</v>
-      </c>
-      <c r="K8" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="L8" t="n">
+      <c r="C9" s="6" t="n">
+        <v>99614.74000000001</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>43598.35</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>56016.39</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>-376.54</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>-385.26</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>99650.82000000001</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>45527.02</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>54123.8</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>36.08</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>-349.18</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>ZEEL</t>
-        </is>
-      </c>
-      <c r="S8">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>99614.74000000001</v>
-      </c>
-      <c r="D9" t="n">
-        <v>46272.98</v>
-      </c>
-      <c r="E9" t="n">
-        <v>53341.76</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-376.54</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-385.26</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="J9" t="n">
-        <v>18092</v>
-      </c>
-      <c r="K9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>ZEEL</t>
-        </is>
-      </c>
-      <c r="S9">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="n">
-        <v>99650.82000000001</v>
-      </c>
-      <c r="D10" t="n">
-        <v>43598.35</v>
-      </c>
-      <c r="E10" t="n">
-        <v>56052.47</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-349.18</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19130</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="S10">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>99989.69</v>
       </c>
-      <c r="D11" t="n">
-        <v>45527.02</v>
-      </c>
-      <c r="E11" t="n">
-        <v>54462.67</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="D11" s="6" t="n">
+        <v>40814.38</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>59175.31</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>338.87</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>0.34</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="7" t="n">
         <v>-10.31</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="7" t="n">
         <v>-0.01</v>
       </c>
-      <c r="J11" t="n">
-        <v>16592</v>
-      </c>
-      <c r="K11" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>99942.91</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>37792.68</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>62150.23</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>-46.78</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>-57.09</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="L11" t="n">
-        <v>8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="O11" t="n">
-        <v>5</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="S11">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="n">
-        <v>99942.91</v>
-      </c>
-      <c r="D12" t="n">
-        <v>40814.38</v>
-      </c>
-      <c r="E12" t="n">
-        <v>59128.53</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>-46.78</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-57.09</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="J12" t="n">
-        <v>14966</v>
-      </c>
-      <c r="K12" t="n">
-        <v>14</v>
-      </c>
-      <c r="L12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.68</v>
-      </c>
-      <c r="O12" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>ZEEL</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="S12">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>100355.31</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>37792.68</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>62562.63</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>412.4</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>0.41</v>
       </c>
       <c r="H13" s="7" t="n">
@@ -7763,56 +6575,29 @@
       <c r="I13" s="7" t="n">
         <v>0.36</v>
       </c>
-      <c r="J13" t="n">
-        <v>6828</v>
-      </c>
-      <c r="K13" t="n">
-        <v>16</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>CAUTIOUS</t>
-        </is>
-      </c>
-      <c r="S13">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="6" t="n">
         <v>101109.37</v>
       </c>
-      <c r="D14" t="n">
-        <v>37310.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>63798.97</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="D14" s="6" t="n">
+        <v>35268.71</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>65840.66</v>
+      </c>
+      <c r="F14" s="7" t="n">
         <v>754.0599999999999</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="H14" s="7" t="n">
@@ -7821,159 +6606,161 @@
       <c r="I14" s="7" t="n">
         <v>1.11</v>
       </c>
-      <c r="J14" t="n">
-        <v>6318</v>
-      </c>
-      <c r="K14" t="n">
-        <v>18</v>
-      </c>
-      <c r="L14" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>100913.3</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>32844.48</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>68068.82000000001</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>-196.07</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>913.3</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>99787</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>33468.05</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>66318.95</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>-1126.3</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>-213</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>100260.21</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>35118.4</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>65141.81</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>473.21</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>260.21</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>100877.64</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>37420.54</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>63457.1</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>617.4299999999999</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>877.64</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>6855</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N14" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="N18" s="6" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="O18" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>CAUTIOUS</t>
         </is>
       </c>
-      <c r="S14">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="n">
-        <v>100913.3</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35268.71</v>
-      </c>
-      <c r="E15" t="n">
-        <v>65644.59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>-196.07</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>913.3</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="J15" t="n">
-        <v>12302</v>
-      </c>
-      <c r="K15" t="n">
-        <v>17</v>
-      </c>
-      <c r="L15" t="n">
-        <v>5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="S15">
-        <f>FALSE()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="115" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B16" s="110" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" s="110" t="n">
-        <v>99787</v>
-      </c>
-      <c r="D16" s="110" t="n">
-        <v>33468.05</v>
-      </c>
-      <c r="E16" s="110" t="n">
-        <v>66318.95</v>
-      </c>
-      <c r="F16" s="111" t="n">
-        <v>-1126.3</v>
-      </c>
-      <c r="G16" s="111" t="n">
-        <v>-0.213</v>
-      </c>
-      <c r="H16" s="111" t="n">
-        <v>-213</v>
-      </c>
-      <c r="I16" s="111" t="n">
-        <v>-0.213</v>
-      </c>
-      <c r="J16" s="110" t="n">
-        <v>7484</v>
-      </c>
-      <c r="K16" s="110" t="n">
-        <v>16</v>
-      </c>
-      <c r="L16" s="110" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" s="110" t="n">
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="N16" s="110" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O16" s="110" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P16" s="110" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="Q16" s="65" t="n"/>
-      <c r="R16" s="65" t="n"/>
-      <c r="S16" s="65" t="b">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -7983,18 +6770,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:U17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -8006,7 +6796,7 @@
     <col width="35" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
@@ -8113,7 +6903,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
@@ -8128,7 +6918,7 @@
         <v>1845</v>
       </c>
       <c r="D2" t="n">
-        <v>1903.4</v>
+        <v>1935.5</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -8137,13 +6927,13 @@
         <v>3690</v>
       </c>
       <c r="G2" t="n">
-        <v>3806.8</v>
+        <v>3871</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>116.8</v>
+        <v>181</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>3.17</v>
+        <v>4.91</v>
       </c>
       <c r="J2" t="n">
         <v>1715.85</v>
@@ -8154,13 +6944,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
         <v>6.7</v>
       </c>
       <c r="N2" t="n">
-        <v>7.45</v>
+        <v>7.46</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -8168,7 +6958,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -8189,7 +6979,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>PRESTIGE</t>
@@ -8204,7 +6994,7 @@
         <v>1504.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1673.3</v>
+        <v>1733.2</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -8213,30 +7003,30 @@
         <v>3008.6</v>
       </c>
       <c r="G3" t="n">
-        <v>3346.6</v>
+        <v>3466.4</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>338</v>
+        <v>457.8</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>11.23</v>
+        <v>15.22</v>
       </c>
       <c r="J3" t="n">
-        <v>1459.17</v>
+        <v>1399</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M3" t="n">
         <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>6.35</v>
+        <v>6.75</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -8244,7 +7034,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -8265,7 +7055,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>CIPLA</t>
@@ -8280,7 +7070,7 @@
         <v>1422.8</v>
       </c>
       <c r="D4" t="n">
-        <v>1451.8</v>
+        <v>1439.4</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -8289,13 +7079,13 @@
         <v>2845.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2903.6</v>
+        <v>2878.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>58</v>
+        <v>33.2</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.04</v>
+        <v>1.17</v>
       </c>
       <c r="J4" t="n">
         <v>1280.52</v>
@@ -8306,7 +7096,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
         <v>7.05</v>
@@ -8341,7 +7131,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>SBIN</t>
@@ -8356,7 +7146,7 @@
         <v>1024</v>
       </c>
       <c r="D5" t="n">
-        <v>1038.1</v>
+        <v>1036</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -8365,13 +7155,13 @@
         <v>4096</v>
       </c>
       <c r="G5" t="n">
-        <v>4152.4</v>
+        <v>4144</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>56.4</v>
+        <v>48</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="J5" t="n">
         <v>993.28</v>
@@ -8382,13 +7172,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M5" t="n">
         <v>7.03</v>
       </c>
       <c r="N5" t="n">
-        <v>6.3</v>
+        <v>7.12</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -8396,7 +7186,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -8417,7 +7207,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>HFCL</t>
@@ -8432,7 +7222,7 @@
         <v>202</v>
       </c>
       <c r="D6" t="n">
-        <v>226.04</v>
+        <v>217.25</v>
       </c>
       <c r="E6" t="n">
         <v>24</v>
@@ -8441,13 +7231,13 @@
         <v>4848</v>
       </c>
       <c r="G6" t="n">
-        <v>5424.96</v>
+        <v>5214</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>576.96</v>
+        <v>366</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>11.9</v>
+        <v>7.55</v>
       </c>
       <c r="J6" t="n">
         <v>195.94</v>
@@ -8458,21 +7248,21 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M6" t="n">
         <v>6.85</v>
       </c>
       <c r="N6" t="n">
-        <v>5.8</v>
+        <v>6.29</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -8493,7 +7283,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
@@ -8508,7 +7298,7 @@
         <v>1340.6</v>
       </c>
       <c r="D7" t="n">
-        <v>1414.7</v>
+        <v>1401.2</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -8517,13 +7307,13 @@
         <v>4021.8</v>
       </c>
       <c r="G7" t="n">
-        <v>4244.1</v>
+        <v>4203.6</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>222.3</v>
+        <v>181.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>5.53</v>
+        <v>4.52</v>
       </c>
       <c r="J7" t="n">
         <v>1300.38</v>
@@ -8534,13 +7324,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M7" t="n">
         <v>6.37</v>
       </c>
       <c r="N7" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -8569,40 +7359,40 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1331.9</v>
+        <v>301.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1354.6</v>
+        <v>330.1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>2663.8</v>
+        <v>3916.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2709.2</v>
+        <v>4291.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>45.4</v>
+        <v>374.4</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.7</v>
+        <v>9.56</v>
       </c>
       <c r="J8" t="n">
-        <v>1291.94</v>
+        <v>292.26</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -8610,165 +7400,165 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="N8" t="n">
-        <v>8.039999999999999</v>
+        <v>5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>New Age Tech</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ACCUMULATE 💚</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/NYKAA:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2665</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2809.9</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2665</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2809.9</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2478.45</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="N9" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="P9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>New Age Tech</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>ACCUMULATE 💚</t>
         </is>
       </c>
-      <c r="S8" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance/quote/DRREDDY:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NYKAA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>301.3</v>
-      </c>
-      <c r="D9" t="n">
-        <v>315.2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>13</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3916.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4097.6</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>180.7</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="J9" t="n">
-        <v>292.26</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/CARTRADE:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>793.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>824.95</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3967.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4124.75</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>157.25</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="J10" t="n">
+        <v>769.6900000000001</v>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>TIGHT</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>10</v>
       </c>
-      <c r="M9" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>New Age Tech</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>ACCUMULATE 💚</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance/quote/NYKAA:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CARTRADE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2665</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2783.4</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2665</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2783.4</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>118.4</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2585.05</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>9</v>
-      </c>
       <c r="M10" t="n">
-        <v>6.69</v>
+        <v>6.85</v>
       </c>
       <c r="N10" t="n">
-        <v>5.85</v>
+        <v>6.78</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -8780,7 +7570,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>New Age Tech</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -8789,18 +7579,18 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>6.15</v>
+        <v>7.3</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/CARTRADE:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
+          <t>https://www.google.com/finance/quote/HDFCBANK:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8809,28 +7599,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>793.5</v>
+        <v>1964</v>
       </c>
       <c r="D11" t="n">
-        <v>829.3</v>
+        <v>2138.9</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>3967.5</v>
+        <v>1964</v>
       </c>
       <c r="G11" t="n">
-        <v>4146.5</v>
+        <v>2138.9</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>179</v>
+        <v>174.9</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.51</v>
+        <v>8.91</v>
       </c>
       <c r="J11" t="n">
-        <v>769.6900000000001</v>
+        <v>1905.08</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -8838,13 +7628,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>6.85</v>
+        <v>6.21</v>
       </c>
       <c r="N11" t="n">
-        <v>6.95</v>
+        <v>6.48</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -8856,209 +7646,209 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ACCUMULATE 💚</t>
+          <t>HOLD ⚖️</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>7.3</v>
+        <v>6.67</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/HDFCBANK:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+          <t>https://www.google.com/finance/quote/PHOENIXLTD:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1964</v>
+        <v>2186</v>
       </c>
       <c r="D12" t="n">
-        <v>2075.1</v>
+        <v>2150.6</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1964</v>
+        <v>2186</v>
       </c>
       <c r="G12" t="n">
-        <v>2075.1</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>5.66</v>
+        <v>2150.6</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-35.4</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>-1.62</v>
       </c>
       <c r="J12" t="n">
-        <v>1905.08</v>
+        <v>2032.98</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>HOLD ⚖️</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/HINDUNILVR:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1341.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2418</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2683.6</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1172.73</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>TIGHT</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="N12" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="L13" t="n">
+        <v>9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>New Age Tech</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>HOLD ⚖️</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance/quote/PHOENIXLTD:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2186</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2208.8</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2186</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2208.8</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2032.98</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Consumer Staples</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>HOLD ⚖️</t>
-        </is>
-      </c>
       <c r="S13" t="n">
-        <v>6.35</v>
+        <v>6.77</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/HINDUNILVR:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
+          <t>https://www.google.com/finance/quote/PAYTM:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1209</v>
+        <v>2420</v>
       </c>
       <c r="D14" t="n">
-        <v>1246</v>
+        <v>2496.3</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>2418</v>
+        <v>4840</v>
       </c>
       <c r="G14" t="n">
-        <v>2492</v>
+        <v>4992.6</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>74</v>
+        <v>152.6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>3.06</v>
+        <v>3.15</v>
       </c>
       <c r="J14" t="n">
-        <v>1172.73</v>
+        <v>2347.4</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -9069,42 +7859,42 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>6.01</v>
+        <v>6.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5.6</v>
+        <v>6.83</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>New Age Tech</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>HOLD ⚖️</t>
+          <t>ACCUMULATE 💚</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>6.77</v>
+        <v>6.48</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/PAYTM:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
+          <t>https://www.google.com/finance/quote/LUPIN:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9113,104 +7903,104 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2420</v>
+        <v>1890</v>
       </c>
       <c r="D15" t="n">
-        <v>2490.2</v>
+        <v>1920.4</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>4840</v>
+        <v>3780</v>
       </c>
       <c r="G15" t="n">
-        <v>4980.4</v>
+        <v>3840.8</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>140.4</v>
+        <v>60.8</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="J15" t="n">
-        <v>2347.4</v>
+        <v>1757.7</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>TIGHT</t>
+          <t>RISK</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>6.8</v>
+        <v>6.73</v>
       </c>
       <c r="N15" t="n">
-        <v>6.65</v>
+        <v>6.74</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>→</t>
         </is>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ACCUMULATE 💚</t>
+        </is>
+      </c>
+      <c r="S15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://www.google.com/finance/quote/BHARTIARTL:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1457.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1455.2</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>ACCUMULATE 💚</t>
-        </is>
-      </c>
-      <c r="S15" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance/quote/LUPIN:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>BHARTIARTL</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1890</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1925.8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
       <c r="F16" t="n">
-        <v>3780</v>
+        <v>1457.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3851.6</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>1.89</v>
+        <v>1455.2</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>-0.13</v>
       </c>
       <c r="J16" t="n">
-        <v>1833.3</v>
+        <v>1413.39</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -9221,10 +8011,10 @@
         <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>6.73</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
-        <v>6.3</v>
+        <v>7.58</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -9236,7 +8026,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -9245,66 +8035,66 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>6.25</v>
+        <v>6.62</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/BHARTIARTL:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+          <t>https://www.google.com/finance/quote/NESTLEIND:NSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1457.1</v>
+        <v>312</v>
       </c>
       <c r="D17" t="n">
-        <v>1471.8</v>
+        <v>309.75</v>
       </c>
       <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4368</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4336.5</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>-31.5</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J17" t="n">
+        <v>302.64</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TIGHT</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="F17" t="n">
-        <v>1457.1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1471.8</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1413.39</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>6.44</v>
       </c>
       <c r="N17" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -9312,102 +8102,25 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ACCUMULATE 💚</t>
+          <t>HOLD ⚖️</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>6.62</v>
+        <v>6.33</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.google.com/finance/quote/NESTLEIND:NSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DHANUKA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1095</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1073.1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1095</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1073.1</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>-21.9</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1062.15</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>TIGHT</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Agriculture</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>ACCUMULATE 💚</t>
-        </is>
-      </c>
-      <c r="S18" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://www.google.com/finance/quote/DHANUKA:NSE</t>
+          <t>https://www.google.com/finance/quote/BPCL:NSE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -9417,13 +8130,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:P32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="6"/>
-    <col width="12" customWidth="1" min="7" max="8"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
@@ -9434,7 +8151,7 @@
     <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
@@ -9516,7 +8233,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
@@ -9578,7 +8295,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>CARTRADE</t>
@@ -9640,7 +8357,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
@@ -9702,7 +8419,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>SBIN</t>
@@ -9764,7 +8481,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>DLF</t>
@@ -9826,7 +8543,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
@@ -9888,7 +8605,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>LT</t>
@@ -9950,7 +8667,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>HFCL</t>
@@ -10012,7 +8729,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>ZEEL</t>
@@ -10074,7 +8791,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>POLICYBZR</t>
@@ -10136,7 +8853,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
@@ -10198,7 +8915,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>IDEA</t>
@@ -10260,7 +8977,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>CARTRADE</t>
@@ -10322,7 +9039,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>NYKAA</t>
@@ -10384,7 +9101,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>ZEEL</t>
@@ -10446,7 +9163,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
@@ -10508,7 +9225,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>LUPIN</t>
@@ -10570,7 +9287,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
@@ -10632,7 +9349,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>IOC</t>
@@ -10694,7 +9411,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>CARTRADE</t>
@@ -10756,7 +9473,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
@@ -10818,7 +9535,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>ZEEL</t>
@@ -10880,7 +9597,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>AXISBANK</t>
@@ -10942,7 +9659,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
@@ -11004,7 +9721,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>LUPIN</t>
@@ -11066,7 +9783,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>LUPIN</t>
@@ -11128,7 +9845,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>ZEEL</t>
@@ -11190,7 +9907,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>IDEA</t>
@@ -11203,7 +9920,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -11252,9 +9969,194 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DHANUKA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1095</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1036.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1095</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1036.6</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>-58.4</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>-5.33</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SELL-STOP</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>❌ LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>452</v>
+      </c>
+      <c r="E31" t="n">
+        <v>436.55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2260</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2182.75</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>-77.25</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>-3.42</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SELL-STOP</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>❌ LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1331.9</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1269.5</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2663.8</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2539</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>-124.8</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SELL-STOP</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>15</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7.94</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>❌ LOSS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -11265,15 +10167,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="4"/>
-    <col width="8" customWidth="1" min="5" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -11311,1731 +10216,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>🤖  STOCK COUNCIL — MODEL IMPROVEMENT LOG</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>All structural, algorithmic, and data-quality changes made to the trading system (Model A &amp; B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Change / Fix</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>File(s) Modified</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>Root Cause / Reason</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Expected Impact</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Verified ?</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀  SYSTEM RELIABILITY &amp; CRASH RECOVERY  ▶</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Raised COUNCIL_MAX_RETRIES: 3 → 12</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>night_runner.py</t>
-        </is>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>Ollama occasionally returned empty/malformed JSON on first attempt; 3 retries too low for slow LLM calls</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>Fewer council skips; more stocks evaluated per night; GPU warmup handled gracefully</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>Per-bot checkpoint cache (_save_bot_cache)</t>
-        </is>
-      </c>
-      <c r="E6" s="25" t="inlineStr">
-        <is>
-          <t>night_runner.py</t>
-        </is>
-      </c>
-      <c r="F6" s="26" t="inlineStr">
-        <is>
-          <t>Full crash during council (e.g. OOM) lost all partial bot outputs; run had to restart from scratch</t>
-        </is>
-      </c>
-      <c r="G6" s="27" t="inlineStr">
-        <is>
-          <t>Crash recovery resumes from last completed bot; saves ~20-30 min on partial failures</t>
-        </is>
-      </c>
-      <c r="H6" s="28" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀  PORTFOLIO ENGINE &amp; MODEL B  ▶</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>New Feature</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Model B — Daily Conviction Budget engine</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t>portfolio_engine_v2.py
-portfolio_state_v2.json</t>
-        </is>
-      </c>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>Model A lump-sum allocation misses daily opportunities; need incremental deployment</t>
-        </is>
-      </c>
-      <c r="G8" s="35" t="inlineStr">
-        <is>
-          <t>₹10,000/day conviction budget; vanishes if unused; parallel tracking vs Model A for A/B comparison</t>
-        </is>
-      </c>
-      <c r="H8" s="36" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I8" s="37" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀  DATA QUALITY &amp; TICKER FIXES  ▶</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Data Quality</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
-        <is>
-          <t>Fixed 5 Yahoo Finance ticker symbols (false-delisted)</t>
-        </is>
-      </c>
-      <c r="E10" s="25" t="inlineStr">
-        <is>
-          <t>data/price_cache/*.csv</t>
-        </is>
-      </c>
-      <c r="F10" s="26" t="inlineStr">
-        <is>
-          <t>YFinance returned "delisted" for OFSS, PERSISTENT, COFORGE, TRENT, BRIGADE — wrong NS/BO suffix</t>
-        </is>
-      </c>
-      <c r="G10" s="27" t="inlineStr">
-        <is>
-          <t>Correct OHLCV data for 5 high-quality large-caps; GPS scores now accurate for these stocks</t>
-        </is>
-      </c>
-      <c r="H10" s="28" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I10" s="29" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀  SCANNER, PIPELINE &amp; MISSED OPPORTUNITIES  ▶</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>Bug Fix</t>
-        </is>
-      </c>
-      <c r="D12" s="41" t="inlineStr">
-        <is>
-          <t>Sector scanner pool expanded: top 3 → top 10 per sector</t>
-        </is>
-      </c>
-      <c r="E12" s="42" t="inlineStr">
-        <is>
-          <t>scanner/sector_scanner.py  (rank_stocks_in_sector)</t>
-        </is>
-      </c>
-      <c r="F12" s="43" t="inlineStr">
-        <is>
-          <t>scored[:3] hardcoded cap meant orchestrator's n_stocks logic (up to 8) had only 3 candidates; high-GPS stocks like OFSS (GPS 8.05) silently dropped</t>
-        </is>
-      </c>
-      <c r="G12" s="44" t="inlineStr">
-        <is>
-          <t>Orchestrator now sees full candidate pool per sector; n_stocks=6 can actually pick 6 stocks</t>
-        </is>
-      </c>
-      <c r="H12" s="45" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I12" s="46" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>New Feature</t>
-        </is>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
-        <is>
-          <t>GPS Rescue Pass — post-pipeline catch for GPS ≥ 7.5 stocks</t>
-        </is>
-      </c>
-      <c r="E13" s="25" t="inlineStr">
-        <is>
-          <t>night_runner.py  (phase3_council)</t>
-        </is>
-      </c>
-      <c r="F13" s="26" t="inlineStr">
-        <is>
-          <t>Sector cap bug caused OFSS (GPS 8.05, 6.88) and THERMAX (GPS 7.58) to be missed 2 days in a row despite high conviction</t>
-        </is>
-      </c>
-      <c r="G13" s="27" t="inlineStr">
-        <is>
-          <t>Any stock with GPS ≥ 7.5 not already debated gets forced into council after main pipeline; structural gap eliminated</t>
-        </is>
-      </c>
-      <c r="H13" s="28" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I13" s="29" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>New Feature</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Phase 6 — Missed Opportunity Analysis (nightly)</t>
-        </is>
-      </c>
-      <c r="E14" s="33" t="inlineStr">
-        <is>
-          <t>night_runner.py  (phase6_missed_opportunities)
-data/missed_opportunities.json</t>
-        </is>
-      </c>
-      <c r="F14" s="34" t="inlineStr">
-        <is>
-          <t>No visibility into which high-movers were not debated; could not distinguish threshold misses from structural gaps</t>
-        </is>
-      </c>
-      <c r="G14" s="35" t="inlineStr">
-        <is>
-          <t>Top daily movers not debated get fast-mode council run (analytical only); results feed weekly parameter review</t>
-        </is>
-      </c>
-      <c r="H14" s="36" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ◀  DATA INTEGRITY &amp; DATE CORRECTIONS  ▶</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C16" s="39" t="inlineStr">
-        <is>
-          <t>Bug Fix</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>Restored truncated file endings (pre-existing corruption)</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="inlineStr">
-        <is>
-          <t>scanner/sector_scanner.py
-night_runner.py</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="inlineStr">
-        <is>
-          <t>Both files silently truncated mid-line/mid-string (lines 673, 987); likely from a previous session crash</t>
-        </is>
-      </c>
-      <c r="G16" s="27" t="inlineStr">
-        <is>
-          <t>scan_sectors() print loop restored; main() argparse + run_tonight() call restored; both compile clean</t>
-        </is>
-      </c>
-      <c r="H16" s="28" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I16" s="29" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="38" t="n">
-        <v>9</v>
-      </c>
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="inlineStr">
-        <is>
-          <t>Data Quality</t>
-        </is>
-      </c>
-      <c r="D17" s="48" t="inlineStr">
-        <is>
-          <t>Day 14 date corrected: 2026-07-08 → 2026-07-07</t>
-        </is>
-      </c>
-      <c r="E17" s="49" t="inlineStr">
-        <is>
-          <t>data/portfolio_state.json
-portfolio_tracker.xlsx
-(Daily Log rows 82-87, Closed Trades row 29)</t>
-        </is>
-      </c>
-      <c r="F17" s="50" t="inlineStr">
-        <is>
-          <t>Night runner ran on July 7 but system clock / state recorded July 8; duplicate guard would have blocked Day 15</t>
-        </is>
-      </c>
-      <c r="G17" s="51" t="inlineStr">
-        <is>
-          <t>Day 15 (today, July 8) runs cleanly; no false-duplicate detection</t>
-        </is>
-      </c>
-      <c r="H17" s="52" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I17" s="53" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="C18" s="54" t="inlineStr">
-        <is>
-          <t>Model B</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>plan_b_tracker.xlsx regenerated with correct 14-day data</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="inlineStr">
-        <is>
-          <t>plan_b_tracker.xlsx</t>
-        </is>
-      </c>
-      <c r="F18" s="26" t="inlineStr">
-        <is>
-          <t>Previous version had placeholder data and July 4 (Saturday) budget logic errors</t>
-        </is>
-      </c>
-      <c r="G18" s="27" t="inlineStr">
-        <is>
-          <t>Accurate Model B dashboard: ₹10k/day vanishing budget, 14 trading days, A vs B comparison sheet</t>
-        </is>
-      </c>
-      <c r="H18" s="28" t="inlineStr">
-        <is>
-          <t>Live ✅</t>
-        </is>
-      </c>
-      <c r="I18" s="29" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="55" t="inlineStr">
-        <is>
-          <t>IMPACT SUMMARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="56" t="inlineStr">
-        <is>
-          <t>Total Changes Logged</t>
-        </is>
-      </c>
-      <c r="B21" s="57">
-        <f>COUNTA(B4:B19)</f>
-        <v/>
-      </c>
-      <c r="C21" s="69" t="n"/>
-      <c r="D21" s="70" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="56" t="inlineStr">
-        <is>
-          <t>Live / Deployed</t>
-        </is>
-      </c>
-      <c r="B22" s="57">
-        <f>COUNTIF(H4:H19,"Live ✅")</f>
-        <v/>
-      </c>
-      <c r="C22" s="69" t="n"/>
-      <c r="D22" s="70" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="56" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="B23" s="57">
-        <f>COUNTIF(I4:I19,"Yes ✔")</f>
-        <v/>
-      </c>
-      <c r="C23" s="69" t="n"/>
-      <c r="D23" s="70" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="56" t="inlineStr">
-        <is>
-          <t>Bug Fixes</t>
-        </is>
-      </c>
-      <c r="B24" s="57">
-        <f>COUNTIF(C4:C19,"Bug Fix")</f>
-        <v/>
-      </c>
-      <c r="C24" s="69" t="n"/>
-      <c r="D24" s="70" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="56" t="inlineStr">
-        <is>
-          <t>New Features</t>
-        </is>
-      </c>
-      <c r="B25" s="57">
-        <f>COUNTIF(C4:C19,"New Feature")</f>
-        <v/>
-      </c>
-      <c r="C25" s="69" t="n"/>
-      <c r="D25" s="70" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="56" t="inlineStr">
-        <is>
-          <t>GPS Rescue threshold</t>
-        </is>
-      </c>
-      <c r="B26" s="57" t="inlineStr">
-        <is>
-          <t>GPS ≥ 7.5 (hardcoded in night_runner.py)</t>
-        </is>
-      </c>
-      <c r="C26" s="69" t="n"/>
-      <c r="D26" s="70" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="56" t="inlineStr">
-        <is>
-          <t>Sector pool size (current)</t>
-        </is>
-      </c>
-      <c r="B27" s="57" t="inlineStr">
-        <is>
-          <t>10 stocks/sector (was 3)</t>
-        </is>
-      </c>
-      <c r="C27" s="69" t="n"/>
-      <c r="D27" s="70" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="56" t="inlineStr">
-        <is>
-          <t>Model A GPS threshold</t>
-        </is>
-      </c>
-      <c r="B28" s="57" t="inlineStr">
-        <is>
-          <t>6.0  (last reviewed: 2026-07-07)</t>
-        </is>
-      </c>
-      <c r="C28" s="69" t="n"/>
-      <c r="D28" s="70" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="56" t="inlineStr">
-        <is>
-          <t>Next parameter review</t>
-        </is>
-      </c>
-      <c r="B29" s="57" t="inlineStr">
-        <is>
-          <t>Sunday 2026-07-12, 7:00 PM IST</t>
-        </is>
-      </c>
-      <c r="C29" s="69" t="n"/>
-      <c r="D29" s="70" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="B24:D24"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>🛠️  STOCK COUNCIL — OPERATIONS RUNBOOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="73" t="inlineStr">
-        <is>
-          <t>Commands to run for every verified issue — copy-paste into terminal from C:\Users\110575\Desktop\StockCouncil\stock_council\stock_council\</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="74" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="74" t="inlineStr">
-        <is>
-          <t>Issue / Trigger</t>
-        </is>
-      </c>
-      <c r="C3" s="74" t="inlineStr">
-        <is>
-          <t>Command to Run (copy-paste)</t>
-        </is>
-      </c>
-      <c r="D3" s="74" t="inlineStr">
-        <is>
-          <t>What It Does</t>
-        </is>
-      </c>
-      <c r="E3" s="74" t="inlineStr">
-        <is>
-          <t>Verified?</t>
-        </is>
-      </c>
-      <c r="F3" s="74" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  NIGHT RUNNER — STARTUP &amp; NORMAL RUN</t>
-        </is>
-      </c>
-      <c r="B4" s="112" t="n"/>
-      <c r="C4" s="112" t="n"/>
-      <c r="D4" s="112" t="n"/>
-      <c r="E4" s="112" t="n"/>
-      <c r="F4" s="113" t="n"/>
-    </row>
-    <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="77" t="inlineStr">
-        <is>
-          <t>Normal nightly run
-(run after 5 PM IST)</t>
-        </is>
-      </c>
-      <c r="C5" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py</t>
-        </is>
-      </c>
-      <c r="D5" s="79" t="inlineStr">
-        <is>
-          <t>Full 6-phase pipeline:
-Phase1=data, Phase2=accuracy,
-Phase3=council, Phase4=portfolio,
-Phase5=report, Phase6=missed-opp</t>
-        </is>
-      </c>
-      <c r="E5" s="80" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F5" s="81" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="77" t="inlineStr">
-        <is>
-          <t>Faster run — skip missed-opportunity analysis (~45 min saved)</t>
-        </is>
-      </c>
-      <c r="C6" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --skip-missed-opp</t>
-        </is>
-      </c>
-      <c r="D6" s="79" t="inlineStr">
-        <is>
-          <t>Skips Phase 6 (missed opportunity scan). Use when short on time. Core council + portfolio still runs.</t>
-        </is>
-      </c>
-      <c r="E6" s="80" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F6" s="81" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="82" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="83" t="inlineStr">
-        <is>
-          <t>"Already ran today" error
-(duplicate guard triggered)</t>
-        </is>
-      </c>
-      <c r="C7" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --force</t>
-        </is>
-      </c>
-      <c r="D7" s="84" t="inlineStr">
-        <is>
-          <t>Overrides the duplicate-date guard in learning_progress.json. Use ONLY if last run crashed before Phase 5 completed.</t>
-        </is>
-      </c>
-      <c r="E7" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F7" s="86" t="inlineStr">
-        <is>
-          <t>MED ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="77" t="inlineStr">
-        <is>
-          <t>Skip Ollama restart
-(Ollama already warm)</t>
-        </is>
-      </c>
-      <c r="C8" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --no-restart</t>
-        </is>
-      </c>
-      <c r="D8" s="79" t="inlineStr">
-        <is>
-          <t>Skips restarting Ollama at start. Use if you just ran and want a quick second pass.</t>
-        </is>
-      </c>
-      <c r="E8" s="80" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F8" s="81" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="87" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="88" t="inlineStr">
-        <is>
-          <t>Data refresh only
-(no council, no portfolio)</t>
-        </is>
-      </c>
-      <c r="C9" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --data-only</t>
-        </is>
-      </c>
-      <c r="D9" s="89" t="inlineStr">
-        <is>
-          <t>Only runs Phase 1 (price + fundamentals download). Useful to pre-cache data before 5 PM.</t>
-        </is>
-      </c>
-      <c r="E9" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F9" s="91" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="82" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="83" t="inlineStr">
-        <is>
-          <t>Override GPS threshold for tonight</t>
-        </is>
-      </c>
-      <c r="C10" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --gps 5.5</t>
-        </is>
-      </c>
-      <c r="D10" s="84" t="inlineStr">
-        <is>
-          <t>Temporarily lowers GPS filter (default 6.0). More stocks enter council. Replace 5.5 with desired threshold.</t>
-        </is>
-      </c>
-      <c r="E10" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F10" s="86" t="inlineStr">
-        <is>
-          <t>MED ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  SYNTAX / IMPORT ERRORS</t>
-        </is>
-      </c>
-      <c r="B11" s="112" t="n"/>
-      <c r="C11" s="112" t="n"/>
-      <c r="D11" s="112" t="n"/>
-      <c r="E11" s="112" t="n"/>
-      <c r="F11" s="113" t="n"/>
-    </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="87" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="88" t="inlineStr">
-        <is>
-          <t>SyntaxError in night_runner.py
-(e.g. "unterminated string")</t>
-        </is>
-      </c>
-      <c r="C12" s="78" t="inlineStr">
-        <is>
-          <t>python -B -m py_compile night_runner.py</t>
-        </is>
-      </c>
-      <c r="D12" s="89" t="inlineStr">
-        <is>
-          <t>Compiles file without running it. Shows exact line + error. Safe check — no state changes.</t>
-        </is>
-      </c>
-      <c r="E12" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F12" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="87" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="88" t="inlineStr">
-        <is>
-          <t>SyntaxError in sector_scanner.py</t>
-        </is>
-      </c>
-      <c r="C13" s="78" t="inlineStr">
-        <is>
-          <t>python -B -m py_compile scanner/sector_scanner.py</t>
-        </is>
-      </c>
-      <c r="D13" s="89" t="inlineStr">
-        <is>
-          <t>Same compile-check for the sector scanner. Use after any manual edits.</t>
-        </is>
-      </c>
-      <c r="E13" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F13" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="87" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="88" t="inlineStr">
-        <is>
-          <t>Check ALL .py files for syntax errors</t>
-        </is>
-      </c>
-      <c r="C14" s="78" t="inlineStr">
-        <is>
-          <t>python -B -m py_compile bots/*.py
-python -B -m py_compile pipeline/*.py</t>
-        </is>
-      </c>
-      <c r="D14" s="89" t="inlineStr">
-        <is>
-          <t>Batch compile-check all bots and pipeline files. Catches import-level errors before running.</t>
-        </is>
-      </c>
-      <c r="E14" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F14" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="68" customHeight="1">
-      <c r="A15" s="82" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>Duplicate tail in night_runner.py
-(after cat &gt;&gt; double-append)</t>
-        </is>
-      </c>
-      <c r="C15" s="78" t="inlineStr">
-        <is>
-          <t>python -B -m py_compile night_runner.py
--- if error: open file, delete lines after last "if __name__" block --</t>
-        </is>
-      </c>
-      <c r="D15" s="84" t="inlineStr">
-        <is>
-          <t>The file should end at:
-  if __name__ == '__main__':
-      main()
-Delete any lines after this block.</t>
-        </is>
-      </c>
-      <c r="E15" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F15" s="93" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  CORRUPTED JSON STATE FILES</t>
-        </is>
-      </c>
-      <c r="B16" s="112" t="n"/>
-      <c r="C16" s="112" t="n"/>
-      <c r="D16" s="112" t="n"/>
-      <c r="E16" s="112" t="n"/>
-      <c r="F16" s="113" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="87" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="88" t="inlineStr">
-        <is>
-          <t>Verify all 3 state files are valid JSON</t>
-        </is>
-      </c>
-      <c r="C17" s="78" t="inlineStr">
-        <is>
-          <t>python -c "import json; [json.load(open(f'data/{f}')) for f in ['portfolio_state.json','portfolio_state_v2.json','learning_progress.json']]; print('ALL OK')"</t>
-        </is>
-      </c>
-      <c r="D17" s="89" t="inlineStr">
-        <is>
-          <t>Quick check — prints ALL OK or shows which file + line is broken.</t>
-        </is>
-      </c>
-      <c r="E17" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F17" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="82" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="83" t="inlineStr">
-        <is>
-          <t>portfolio_state.json corrupted
-(truncated mid-write)</t>
-        </is>
-      </c>
-      <c r="C18" s="78" t="inlineStr">
-        <is>
-          <t>-- Use repair_jsons.py script --
-python ../repair_jsons.py
-(script is in outputs folder)</t>
-        </is>
-      </c>
-      <c r="D18" s="84" t="inlineStr">
-        <is>
-          <t>Closes truncated JSON, adds missing Day entries from night_report. Always check night_report_{date}.json first for correct values.</t>
-        </is>
-      </c>
-      <c r="E18" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F18" s="86" t="inlineStr">
-        <is>
-          <t>MED ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="87" t="n">
-        <v>13</v>
-      </c>
-      <c r="B19" s="88" t="inlineStr">
-        <is>
-          <t>Check what date the duplicate guard sees
-(will it block tonight's run?)</t>
-        </is>
-      </c>
-      <c r="C19" s="78" t="inlineStr">
-        <is>
-          <t>python -c "import json; d=json.load(open('data/learning_progress.json')); [print(e['date'],'Day',e['day']) for e in d['daily_log'][-3:]]"</t>
-        </is>
-      </c>
-      <c r="D19" s="89" t="inlineStr">
-        <is>
-          <t>Shows last 3 daily_log dates. If today's date is listed, night runner will skip (use --force to override).</t>
-        </is>
-      </c>
-      <c r="E19" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F19" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="87" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="88" t="inlineStr">
-        <is>
-          <t>Find all files referencing a bad date
-(e.g. wrong 2026-07-08 in Day 14)</t>
-        </is>
-      </c>
-      <c r="C20" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">python -c "import subprocess; r=subprocess.run(['grep','-rl','BAD_DATE','data/'],capture_output=True,text=True); print(r.stdout)" </t>
-        </is>
-      </c>
-      <c r="D20" s="89" t="inlineStr">
-        <is>
-          <t>Replace BAD_DATE with the date string to search. Shows which JSON files need fixing.</t>
-        </is>
-      </c>
-      <c r="E20" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F20" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  PORTFOLIO &amp; EXCEL TRACKERS</t>
-        </is>
-      </c>
-      <c r="B21" s="112" t="n"/>
-      <c r="C21" s="112" t="n"/>
-      <c r="D21" s="112" t="n"/>
-      <c r="E21" s="112" t="n"/>
-      <c r="F21" s="113" t="n"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="A22" s="87" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="88" t="inlineStr">
-        <is>
-          <t>Update Excel trackers manually
-(after JSON repair)</t>
-        </is>
-      </c>
-      <c r="C22" s="78" t="inlineStr">
-        <is>
-          <t>python portfolio_excel.py</t>
-        </is>
-      </c>
-      <c r="D22" s="89" t="inlineStr">
-        <is>
-          <t>Regenerates portfolio_tracker.xlsx from portfolio_state.json. Run after repairing state files.</t>
-        </is>
-      </c>
-      <c r="E22" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F22" s="91" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="82" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="83" t="inlineStr">
-        <is>
-          <t>Check portfolio engine without running full council</t>
-        </is>
-      </c>
-      <c r="C23" s="78" t="inlineStr">
-        <is>
-          <t>python run_phase4_manual.py</t>
-        </is>
-      </c>
-      <c r="D23" s="84" t="inlineStr">
-        <is>
-          <t>Runs only Phase 4 (portfolio decisions). Does not call Ollama. Use to re-apply buys/sells from council output.</t>
-        </is>
-      </c>
-      <c r="E23" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F23" s="86" t="inlineStr">
-        <is>
-          <t>MED ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="82" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="83" t="inlineStr">
-        <is>
-          <t>Model B backtest re-run</t>
-        </is>
-      </c>
-      <c r="C24" s="78" t="inlineStr">
-        <is>
-          <t>python run_backtest_v2.py</t>
-        </is>
-      </c>
-      <c r="D24" s="84" t="inlineStr">
-        <is>
-          <t>Rebuilds portfolio_state_v2.json from scratch using all council session JSONs. Run if v2 state gets corrupted.</t>
-        </is>
-      </c>
-      <c r="E24" s="85" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F24" s="86" t="inlineStr">
-        <is>
-          <t>MED ⚠</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  SECTOR SCANNER &amp; GPS ISSUES</t>
-        </is>
-      </c>
-      <c r="B25" s="112" t="n"/>
-      <c r="C25" s="112" t="n"/>
-      <c r="D25" s="112" t="n"/>
-      <c r="E25" s="112" t="n"/>
-      <c r="F25" s="113" t="n"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="97" t="n">
-        <v>18</v>
-      </c>
-      <c r="B26" s="98" t="inlineStr">
-        <is>
-          <t>Test sector scanner standalone
-(check which stocks it picks)</t>
-        </is>
-      </c>
-      <c r="C26" s="78" t="inlineStr">
-        <is>
-          <t>python scan.py</t>
-        </is>
-      </c>
-      <c r="D26" s="99" t="inlineStr">
-        <is>
-          <t>Runs sector scan + GPS filter without council. Shows sector scores, top stocks, GPS values. Fast (~2 min).</t>
-        </is>
-      </c>
-      <c r="E26" s="100" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F26" s="100" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
-      <c r="A27" s="97" t="n">
-        <v>19</v>
-      </c>
-      <c r="B27" s="98" t="inlineStr">
-        <is>
-          <t>High-GPS stock missed by council
-(e.g. OFSS GPS 8.05 not debated)</t>
-        </is>
-      </c>
-      <c r="C27" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --gps 5.5
--- OR --
-GPS Rescue Pass auto-catches GPS ≥ 7.5</t>
-        </is>
-      </c>
-      <c r="D27" s="99" t="inlineStr">
-        <is>
-          <t>GPS Rescue Pass is now active in night_runner.py. Any stock with GPS ≥ 7.5 skipped by sector cap gets force-debated after main pipeline.</t>
-        </is>
-      </c>
-      <c r="E27" s="100" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F27" s="101" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="97" t="n">
-        <v>20</v>
-      </c>
-      <c r="B28" s="98" t="inlineStr">
-        <is>
-          <t>Check sector scanner compiles after edits</t>
-        </is>
-      </c>
-      <c r="C28" s="78" t="inlineStr">
-        <is>
-          <t>python -B -m py_compile scanner/sector_scanner.py</t>
-        </is>
-      </c>
-      <c r="D28" s="99" t="inlineStr">
-        <is>
-          <t>Always run this after editing sector_scanner.py. The file was previously truncated at line 673.</t>
-        </is>
-      </c>
-      <c r="E28" s="100" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F28" s="100" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  OLLAMA / GPU ISSUES</t>
-        </is>
-      </c>
-      <c r="B29" s="112" t="n"/>
-      <c r="C29" s="112" t="n"/>
-      <c r="D29" s="112" t="n"/>
-      <c r="E29" s="112" t="n"/>
-      <c r="F29" s="113" t="n"/>
-    </row>
-    <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="103" t="n">
-        <v>21</v>
-      </c>
-      <c r="B30" s="104" t="inlineStr">
-        <is>
-          <t>Ollama not running / GPU OOM</t>
-        </is>
-      </c>
-      <c r="C30" s="78" t="inlineStr">
-        <is>
-          <t>restart_ollama.bat
--- or --
-taskkill /F /IM ollama.exe &amp;&amp; ollama serve</t>
-        </is>
-      </c>
-      <c r="D30" s="105" t="inlineStr">
-        <is>
-          <t>The .bat file is in the stock_council folder. Kills and restarts Ollama. GPU memory is freed.</t>
-        </is>
-      </c>
-      <c r="E30" s="106" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F30" s="107" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="103" t="n">
-        <v>22</v>
-      </c>
-      <c r="B31" s="104" t="inlineStr">
-        <is>
-          <t>Check if Ollama is responding</t>
-        </is>
-      </c>
-      <c r="C31" s="78" t="inlineStr">
-        <is>
-          <t>curl http://localhost:11434/api/tags</t>
-        </is>
-      </c>
-      <c r="D31" s="105" t="inlineStr">
-        <is>
-          <t>Should return a JSON list of models. If connection refused, Ollama is not running.</t>
-        </is>
-      </c>
-      <c r="E31" s="106" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F31" s="106" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="103" t="n">
-        <v>23</v>
-      </c>
-      <c r="B32" s="104" t="inlineStr">
-        <is>
-          <t>Council crashed mid-run
-(bot checkpoint recovery)</t>
-        </is>
-      </c>
-      <c r="C32" s="78" t="inlineStr">
-        <is>
-          <t>python night_runner.py --no-restart
-(checkpoints auto-loaded)</t>
-        </is>
-      </c>
-      <c r="D32" s="105" t="inlineStr">
-        <is>
-          <t>Per-bot checkpoints saved to data/bot_cache_{date}_{symbol}.json. Next run auto-resumes from last completed bot. No manual action needed.</t>
-        </is>
-      </c>
-      <c r="E32" s="106" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F32" s="107" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶  QUICK DIAGNOSTICS (run anytime)</t>
-        </is>
-      </c>
-      <c r="B33" s="112" t="n"/>
-      <c r="C33" s="112" t="n"/>
-      <c r="D33" s="112" t="n"/>
-      <c r="E33" s="112" t="n"/>
-      <c r="F33" s="113" t="n"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="87" t="n">
-        <v>24</v>
-      </c>
-      <c r="B34" s="88" t="inlineStr">
-        <is>
-          <t>What day is the system on?</t>
-        </is>
-      </c>
-      <c r="C34" s="78" t="inlineStr">
-        <is>
-          <t>python -c "import json; d=json.load(open('data/portfolio_state.json')); print('Model A Day:',d['day'],'| Cash:',d['cash'])"</t>
-        </is>
-      </c>
-      <c r="D34" s="89" t="inlineStr">
-        <is>
-          <t>Prints current day number and cash from Model A state.</t>
-        </is>
-      </c>
-      <c r="E34" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F34" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="87" t="n">
-        <v>25</v>
-      </c>
-      <c r="B35" s="88" t="inlineStr">
-        <is>
-          <t>What did last night's run produce?</t>
-        </is>
-      </c>
-      <c r="C35" s="78" t="inlineStr">
-        <is>
-          <t>python -c "import json,glob,os; f=max(glob.glob('reports/nightly/*.json'),key=os.path.getmtime); print(open(f).read())"</t>
-        </is>
-      </c>
-      <c r="D35" s="89" t="inlineStr">
-        <is>
-          <t>Prints the most recent night report JSON (date, day, accuracy, stocks debated, portfolio value).</t>
-        </is>
-      </c>
-      <c r="E35" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F35" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="87" t="n">
-        <v>26</v>
-      </c>
-      <c r="B36" s="88" t="inlineStr">
-        <is>
-          <t>How many stocks were missed last night?</t>
-        </is>
-      </c>
-      <c r="C36" s="78" t="inlineStr">
-        <is>
-          <t>python -c "import json; d=json.load(open('data/missed_opportunities.json')); e=d[-1]; print(e['date'],'|',len(e.get('missed_stocks',[])),'missed | debated:',e.get('debated_count'))"</t>
-        </is>
-      </c>
-      <c r="D36" s="89" t="inlineStr">
-        <is>
-          <t>Shows last night's missed opportunity summary.</t>
-        </is>
-      </c>
-      <c r="E36" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F36" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="87" t="n">
-        <v>27</v>
-      </c>
-      <c r="B37" s="88" t="inlineStr">
-        <is>
-          <t>Check trading calendar — is today a trading day?</t>
-        </is>
-      </c>
-      <c r="C37" s="78" t="inlineStr">
-        <is>
-          <t>python -c "from trading_calendar import get_trading_date; print(get_trading_date())"</t>
-        </is>
-      </c>
-      <c r="D37" s="89" t="inlineStr">
-        <is>
-          <t>Prints today's effective trading date. If today is a holiday/weekend, shows last trading day.</t>
-        </is>
-      </c>
-      <c r="E37" s="90" t="inlineStr">
-        <is>
-          <t>Yes ✔</t>
-        </is>
-      </c>
-      <c r="F37" s="90" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A25:F25"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>